--- a/pav_3g_results_nodal.xlsx
+++ b/pav_3g_results_nodal.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,13 +490,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G2" t="n">
-        <v>175.0122446297537</v>
+        <v>173.2558736567367</v>
       </c>
       <c r="H2" t="n">
-        <v>1.570385316679004</v>
+        <v>1.555633916081879</v>
       </c>
       <c r="I2" t="n">
-        <v>180.8354183511236</v>
+        <v>179.0206077340696</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G3" t="n">
-        <v>222.093703762316</v>
+        <v>220.2449968487516</v>
       </c>
       <c r="H3" t="n">
-        <v>1.313863758584773</v>
+        <v>1.301503222563862</v>
       </c>
       <c r="I3" t="n">
-        <v>757.4603053342191</v>
+        <v>750.1582697139361</v>
       </c>
     </row>
     <row r="4">
@@ -548,13 +548,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G4" t="n">
-        <v>251.2343935383294</v>
+        <v>249.179314656966</v>
       </c>
       <c r="H4" t="n">
-        <v>1.064319297938676</v>
+        <v>1.054281513328235</v>
       </c>
       <c r="I4" t="n">
-        <v>1725.381238240946</v>
+        <v>1709.384331150597</v>
       </c>
     </row>
     <row r="5">
@@ -577,13 +577,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G5" t="n">
-        <v>249.423522340056</v>
+        <v>247.1163239756096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8292023139422671</v>
+        <v>0.8213529742594431</v>
       </c>
       <c r="I5" t="n">
-        <v>2804.581349572092</v>
+        <v>2779.200866389687</v>
       </c>
     </row>
     <row r="6">
@@ -606,13 +606,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G6" t="n">
-        <v>259.1901903256966</v>
+        <v>256.6022971915266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6163706244442982</v>
+        <v>0.6105081984086916</v>
       </c>
       <c r="I6" t="n">
-        <v>3826.863154162942</v>
+        <v>3792.443660617778</v>
       </c>
     </row>
     <row r="7">
@@ -635,13 +635,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G7" t="n">
-        <v>268.8772083745512</v>
+        <v>266.0038040611628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4310773999481093</v>
+        <v>0.4269544869354982</v>
       </c>
       <c r="I7" t="n">
-        <v>4774.045391662922</v>
+        <v>4730.842605900297</v>
       </c>
     </row>
     <row r="8">
@@ -664,13 +664,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G8" t="n">
-        <v>275.5460361003784</v>
+        <v>272.3871206298254</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2767909289983213</v>
+        <v>0.2741272839062694</v>
       </c>
       <c r="I8" t="n">
-        <v>5651.632708626566</v>
+        <v>5599.816547950893</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G9" t="n">
-        <v>285.7700884429001</v>
+        <v>282.4017131910433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1559267540560089</v>
+        <v>0.1544163261832618</v>
       </c>
       <c r="I9" t="n">
-        <v>6422.261358148798</v>
+        <v>6362.401101160278</v>
       </c>
     </row>
     <row r="10">
@@ -722,13 +722,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G10" t="n">
-        <v>310.5902366509021</v>
+        <v>306.7506264789972</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07316208359586489</v>
+        <v>0.07244884092919311</v>
       </c>
       <c r="I10" t="n">
-        <v>6939.687666983355</v>
+        <v>6873.810232000021</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G11" t="n">
-        <v>316.6519150685446</v>
+        <v>312.4122327334245</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01760028951844459</v>
+        <v>0.01742748927737196</v>
       </c>
       <c r="I11" t="n">
-        <v>7574.011062906781</v>
+        <v>7500.615021929207</v>
       </c>
     </row>
     <row r="12">
@@ -780,13 +780,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.470200626034966</v>
+        <v>-12.70530093905245</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>8042.201570596136</v>
+        <v>7963.515763881711</v>
       </c>
     </row>
     <row r="13">
@@ -809,13 +809,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G13" t="n">
-        <v>316.4765292217521</v>
+        <v>312.2373670356568</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01761218883289411</v>
+        <v>0.01743931926273443</v>
       </c>
       <c r="I13" t="n">
-        <v>7578.617293307429</v>
+        <v>7505.198224362017</v>
       </c>
     </row>
     <row r="14">
@@ -838,13 +838,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G14" t="n">
-        <v>310.4525370000481</v>
+        <v>306.6134958703604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07322036407967164</v>
+        <v>0.07250675781366335</v>
       </c>
       <c r="I14" t="n">
-        <v>6945.375081410706</v>
+        <v>6879.464369932262</v>
       </c>
     </row>
     <row r="15">
@@ -867,13 +867,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G15" t="n">
-        <v>285.8340165441664</v>
+        <v>282.4660051849108</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1560769887523364</v>
+        <v>0.1545655533239335</v>
       </c>
       <c r="I15" t="n">
-        <v>6427.390927548037</v>
+        <v>6367.502396515479</v>
       </c>
     </row>
     <row r="16">
@@ -896,13 +896,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G16" t="n">
-        <v>275.5382703219476</v>
+        <v>272.3797213132593</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2770803374919985</v>
+        <v>0.2744147160035841</v>
       </c>
       <c r="I16" t="n">
-        <v>5655.971741421592</v>
+        <v>5604.133219106677</v>
       </c>
     </row>
     <row r="17">
@@ -925,13 +925,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G17" t="n">
-        <v>268.9338646196583</v>
+        <v>266.0607935717079</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4315482463607668</v>
+        <v>0.4274221044073092</v>
       </c>
       <c r="I17" t="n">
-        <v>4777.752341286987</v>
+        <v>4734.530865038673</v>
       </c>
     </row>
     <row r="18">
@@ -954,13 +954,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G18" t="n">
-        <v>259.2332626855415</v>
+        <v>256.6456696258964</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6170623473856358</v>
+        <v>0.6111951798511805</v>
       </c>
       <c r="I18" t="n">
-        <v>3829.863976279769</v>
+        <v>3795.429546170855</v>
       </c>
     </row>
     <row r="19">
@@ -983,13 +983,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G19" t="n">
-        <v>249.4921662742798</v>
+        <v>247.1852242682867</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8301501560122549</v>
+        <v>0.8222943325072772</v>
       </c>
       <c r="I19" t="n">
-        <v>2806.812004537444</v>
+        <v>2781.420490685389</v>
       </c>
     </row>
     <row r="20">
@@ -1012,13 +1012,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G20" t="n">
-        <v>251.2638234148226</v>
+        <v>249.2089720180235</v>
       </c>
       <c r="H20" t="n">
-        <v>1.06555460677204</v>
+        <v>1.055508384592045</v>
       </c>
       <c r="I20" t="n">
-        <v>1726.781617422525</v>
+        <v>1710.777804451789</v>
       </c>
     </row>
     <row r="21">
@@ -1041,13 +1041,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G21" t="n">
-        <v>222.1462024803066</v>
+        <v>220.2977527191311</v>
       </c>
       <c r="H21" t="n">
-        <v>1.315403179277943</v>
+        <v>1.30303214915135</v>
       </c>
       <c r="I21" t="n">
-        <v>758.0860525484915</v>
+        <v>750.7809127145758</v>
       </c>
     </row>
     <row r="22">
@@ -1070,13 +1070,13 @@
         <v>0.050000027</v>
       </c>
       <c r="G22" t="n">
-        <v>175.0694916177185</v>
+        <v>173.3132649314452</v>
       </c>
       <c r="H22" t="n">
-        <v>1.572225661875605</v>
+        <v>1.557461763817298</v>
       </c>
       <c r="I22" t="n">
-        <v>180.9722551925173</v>
+        <v>179.1568143574735</v>
       </c>
     </row>
   </sheetData>

--- a/pav_3g_results_nodal.xlsx
+++ b/pav_3g_results_nodal.xlsx
@@ -484,19 +484,19 @@
         <v>4.829657877013845</v>
       </c>
       <c r="E2" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000005</v>
       </c>
       <c r="F2" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="G2" t="n">
         <v>173.2558736567367</v>
       </c>
       <c r="H2" t="n">
-        <v>1.555633916081879</v>
+        <v>0.564307504482438</v>
       </c>
       <c r="I2" t="n">
-        <v>179.0206077340696</v>
+        <v>226.4536058390559</v>
       </c>
     </row>
     <row r="3">
@@ -513,19 +513,19 @@
         <v>5.362333615658589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000003</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000006</v>
       </c>
       <c r="G3" t="n">
         <v>220.2449968487516</v>
       </c>
       <c r="H3" t="n">
-        <v>1.301503222563862</v>
+        <v>0.4587077446653787</v>
       </c>
       <c r="I3" t="n">
-        <v>750.1582697139361</v>
+        <v>693.4083793665138</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         <v>5.894978229286525</v>
       </c>
       <c r="E4" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.050000027</v>
+        <v>0.0865715180552644</v>
       </c>
       <c r="G4" t="n">
         <v>249.179314656966</v>
       </c>
       <c r="H4" t="n">
-        <v>1.054281513328235</v>
+        <v>0.3598380430089402</v>
       </c>
       <c r="I4" t="n">
-        <v>1709.384331150597</v>
+        <v>1190.547185884802</v>
       </c>
     </row>
     <row r="5">
@@ -571,19 +571,19 @@
         <v>6.650791291425358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.050000027</v>
+        <v>0.08302206390311846</v>
       </c>
       <c r="G5" t="n">
         <v>247.1163239756096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8213529742594431</v>
+        <v>0.2714256432859262</v>
       </c>
       <c r="I5" t="n">
-        <v>2779.200866389687</v>
+        <v>1562.284645094003</v>
       </c>
     </row>
     <row r="6">
@@ -600,19 +600,19 @@
         <v>7.472515608156249</v>
       </c>
       <c r="E6" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.050000027</v>
+        <v>0.1261556073701416</v>
       </c>
       <c r="G6" t="n">
         <v>256.6022971915266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6105081984086916</v>
+        <v>0.1956592807693321</v>
       </c>
       <c r="I6" t="n">
-        <v>3792.443660617778</v>
+        <v>1803.060169400458</v>
       </c>
     </row>
     <row r="7">
@@ -629,19 +629,19 @@
         <v>8.29423992488714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.050000027</v>
+        <v>0.1196772306616322</v>
       </c>
       <c r="G7" t="n">
         <v>266.0038040611628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4269544869354982</v>
+        <v>0.1329977926089607</v>
       </c>
       <c r="I7" t="n">
-        <v>4730.842605900297</v>
+        <v>1964.457485092366</v>
       </c>
     </row>
     <row r="8">
@@ -658,19 +658,19 @@
         <v>9.115964242618032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>0.050000027</v>
+        <v>0.1602717257350383</v>
       </c>
       <c r="G8" t="n">
         <v>272.3871206298254</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2741272839062694</v>
+        <v>0.08318388305524235</v>
       </c>
       <c r="I8" t="n">
-        <v>5599.816547950893</v>
+        <v>2080.96770843391</v>
       </c>
     </row>
     <row r="9">
@@ -687,19 +687,19 @@
         <v>9.937688559348924</v>
       </c>
       <c r="E9" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.050000027</v>
+        <v>0.1508949334013102</v>
       </c>
       <c r="G9" t="n">
         <v>282.4017131910433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1544163261832618</v>
+        <v>0.04573768641131502</v>
       </c>
       <c r="I9" t="n">
-        <v>6362.401101160278</v>
+        <v>2274.469686193753</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>10.78953326634482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.050000027</v>
+        <v>0.1847827041768386</v>
       </c>
       <c r="G10" t="n">
         <v>306.7506264789972</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07244884092919311</v>
+        <v>0.0210434395004962</v>
       </c>
       <c r="I10" t="n">
-        <v>6873.810232000021</v>
+        <v>2588.968362117239</v>
       </c>
     </row>
     <row r="11">
@@ -745,19 +745,19 @@
         <v>12.27959952098016</v>
       </c>
       <c r="E11" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="F11" t="n">
-        <v>0.050000027</v>
+        <v>0.1833959534196968</v>
       </c>
       <c r="G11" t="n">
         <v>312.4122327334245</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01742748927737196</v>
+        <v>0.004945392959949732</v>
       </c>
       <c r="I11" t="n">
-        <v>7500.615021929207</v>
+        <v>2265.804301883248</v>
       </c>
     </row>
     <row r="12">
@@ -774,10 +774,10 @@
         <v>12.29250535794931</v>
       </c>
       <c r="E12" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.050000027</v>
+        <v>0.2076483363435291</v>
       </c>
       <c r="G12" t="n">
         <v>-12.70530093905245</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7963.515763881711</v>
+        <v>2381.00381407354</v>
       </c>
     </row>
     <row r="13">
@@ -803,19 +803,19 @@
         <v>12.27348826768008</v>
       </c>
       <c r="E13" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="F13" t="n">
-        <v>0.050000027</v>
+        <v>0.1834522276756144</v>
       </c>
       <c r="G13" t="n">
         <v>312.2373670356568</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01743931926273443</v>
+        <v>0.004948010899307982</v>
       </c>
       <c r="I13" t="n">
-        <v>7505.198224362017</v>
+        <v>2266.733301637856</v>
       </c>
     </row>
     <row r="14">
@@ -832,19 +832,19 @@
         <v>10.78281312271594</v>
       </c>
       <c r="E14" t="n">
-        <v>0.050000027</v>
+        <v>0.0393701</v>
       </c>
       <c r="F14" t="n">
-        <v>0.050000027</v>
+        <v>0.1848225771723788</v>
       </c>
       <c r="G14" t="n">
         <v>306.6134958703604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07250675781366335</v>
+        <v>0.0210564619850966</v>
       </c>
       <c r="I14" t="n">
-        <v>6879.464369932262</v>
+        <v>2590.843850576393</v>
       </c>
     </row>
     <row r="15">
@@ -861,19 +861,19 @@
         <v>9.932764763690075</v>
       </c>
       <c r="E15" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>0.050000027</v>
+        <v>0.1509502445468758</v>
       </c>
       <c r="G15" t="n">
         <v>282.4660051849108</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1545655533239335</v>
+        <v>0.04577278403900064</v>
       </c>
       <c r="I15" t="n">
-        <v>6367.502396515479</v>
+        <v>2276.071403709836</v>
       </c>
     </row>
     <row r="16">
@@ -890,19 +890,19 @@
         <v>9.111449356179994</v>
       </c>
       <c r="E16" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>0.050000027</v>
+        <v>0.160296068186784</v>
       </c>
       <c r="G16" t="n">
         <v>272.3797213132593</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2744147160035841</v>
+        <v>0.08325352048784469</v>
       </c>
       <c r="I16" t="n">
-        <v>5604.133219106677</v>
+        <v>2082.017918549884</v>
       </c>
     </row>
     <row r="17">
@@ -919,19 +919,19 @@
         <v>8.290133948669915</v>
       </c>
       <c r="E17" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.050000027</v>
+        <v>0.1197257689146712</v>
       </c>
       <c r="G17" t="n">
         <v>266.0607935717079</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4274221044073092</v>
+        <v>0.1331143506131333</v>
       </c>
       <c r="I17" t="n">
-        <v>4734.530865038673</v>
+        <v>1965.462062979232</v>
       </c>
     </row>
     <row r="18">
@@ -948,19 +948,19 @@
         <v>7.468818541159835</v>
       </c>
       <c r="E18" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.050000027</v>
+        <v>0.1261718447549538</v>
       </c>
       <c r="G18" t="n">
         <v>256.6456696258964</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6111951798511805</v>
+        <v>0.1958356894151815</v>
       </c>
       <c r="I18" t="n">
-        <v>3795.429546170855</v>
+        <v>1803.994218841279</v>
       </c>
     </row>
     <row r="19">
@@ -977,19 +977,19 @@
         <v>6.647503134649754</v>
       </c>
       <c r="E19" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000003</v>
       </c>
       <c r="F19" t="n">
-        <v>0.050000027</v>
+        <v>0.08306175713833551</v>
       </c>
       <c r="G19" t="n">
         <v>247.1852242682867</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8222943325072772</v>
+        <v>0.2716751788558065</v>
       </c>
       <c r="I19" t="n">
-        <v>2781.420490685389</v>
+        <v>1563.109586022101</v>
       </c>
     </row>
     <row r="20">
@@ -1006,19 +1006,19 @@
         <v>5.892053390707112</v>
       </c>
       <c r="E20" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.050000027</v>
+        <v>0.08657831020314619</v>
       </c>
       <c r="G20" t="n">
         <v>249.2089720180235</v>
       </c>
       <c r="H20" t="n">
-        <v>1.055508384592045</v>
+        <v>0.3601746369066422</v>
       </c>
       <c r="I20" t="n">
-        <v>1710.777804451789</v>
+        <v>1191.193782680512</v>
       </c>
     </row>
     <row r="21">
@@ -1035,19 +1035,19 @@
         <v>5.359673835222307</v>
       </c>
       <c r="E21" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000003</v>
       </c>
       <c r="F21" t="n">
-        <v>0.050000027</v>
+        <v>0.0393990351620512</v>
       </c>
       <c r="G21" t="n">
         <v>220.2977527191311</v>
       </c>
       <c r="H21" t="n">
-        <v>1.30303214915135</v>
+        <v>0.4591414724584371</v>
       </c>
       <c r="I21" t="n">
-        <v>750.7809127145758</v>
+        <v>693.7824515056474</v>
       </c>
     </row>
     <row r="22">
@@ -1064,19 +1064,19 @@
         <v>4.827294278737503</v>
       </c>
       <c r="E22" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000005</v>
       </c>
       <c r="F22" t="n">
-        <v>0.050000027</v>
+        <v>0.03937010000000003</v>
       </c>
       <c r="G22" t="n">
         <v>173.3132649314452</v>
       </c>
       <c r="H22" t="n">
-        <v>1.557461763817298</v>
+        <v>0.5648400741826339</v>
       </c>
       <c r="I22" t="n">
-        <v>179.1568143574735</v>
+        <v>226.6145019852947</v>
       </c>
     </row>
   </sheetData>

--- a/pav_3g_results_nodal.xlsx
+++ b/pav_3g_results_nodal.xlsx
@@ -484,19 +484,19 @@
         <v>4.829657877013845</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03937010000000005</v>
+        <v>0.00393701</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0393701</v>
+        <v>0.0293901382902723</v>
       </c>
       <c r="G2" t="n">
         <v>173.2558736567367</v>
       </c>
       <c r="H2" t="n">
-        <v>0.564307504482438</v>
+        <v>0.5703829667906931</v>
       </c>
       <c r="I2" t="n">
-        <v>226.4536058390559</v>
+        <v>1938.799597043143</v>
       </c>
     </row>
     <row r="3">
@@ -513,19 +513,19 @@
         <v>5.362333615658589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03937010000000003</v>
+        <v>0.00393701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03937010000000006</v>
+        <v>0.04939784984689856</v>
       </c>
       <c r="G3" t="n">
         <v>220.2449968487516</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4587077446653787</v>
+        <v>0.4629172790768787</v>
       </c>
       <c r="I3" t="n">
-        <v>693.4083793665138</v>
+        <v>5923.148152017651</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         <v>5.894978229286525</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03937010000000003</v>
+        <v>0.00393701000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0865715180552644</v>
+        <v>0.07892526879213922</v>
       </c>
       <c r="G4" t="n">
         <v>249.179314656966</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3598380430089402</v>
+        <v>0.3625969743020216</v>
       </c>
       <c r="I4" t="n">
-        <v>1190.547185884802</v>
+        <v>9402.014782516082</v>
       </c>
     </row>
     <row r="5">
@@ -571,19 +571,19 @@
         <v>6.650791291425358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0393701</v>
+        <v>0.004781354515402122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08302206390311846</v>
+        <v>0.09412376043735846</v>
       </c>
       <c r="G5" t="n">
         <v>247.1163239756096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2714256432859262</v>
+        <v>0.2731573945564221</v>
       </c>
       <c r="I5" t="n">
-        <v>1562.284645094003</v>
+        <v>10442.73600582233</v>
       </c>
     </row>
     <row r="6">
@@ -600,19 +600,19 @@
         <v>7.472515608156249</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03937010000000001</v>
+        <v>0.006833490371727782</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1261556073701416</v>
+        <v>0.1181365525616161</v>
       </c>
       <c r="G6" t="n">
         <v>256.6022971915266</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1956592807693321</v>
+        <v>0.1966380524413888</v>
       </c>
       <c r="I6" t="n">
-        <v>1803.060169400458</v>
+        <v>10442.73600582098</v>
       </c>
     </row>
     <row r="7">
@@ -629,19 +629,19 @@
         <v>8.29423992488714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03937010000000002</v>
+        <v>0.005505614395758407</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1196772306616322</v>
+        <v>0.1303519985848394</v>
       </c>
       <c r="G7" t="n">
         <v>266.0038040611628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1329977926089607</v>
+        <v>0.1334481507327958</v>
       </c>
       <c r="I7" t="n">
-        <v>1964.457485092366</v>
+        <v>10442.73600581492</v>
       </c>
     </row>
     <row r="8">
@@ -658,19 +658,19 @@
         <v>9.115964242618032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03937010000000002</v>
+        <v>0.009291141763754424</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1602717257350383</v>
+        <v>0.1519342674654917</v>
       </c>
       <c r="G8" t="n">
         <v>272.3871206298254</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08318388305524235</v>
+        <v>0.08330644730846357</v>
       </c>
       <c r="I8" t="n">
-        <v>2080.96770843391</v>
+        <v>10442.73600580989</v>
       </c>
     </row>
     <row r="9">
@@ -687,19 +687,19 @@
         <v>9.937688559348924</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0393701</v>
+        <v>0.005612545325295521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1508949334013102</v>
+        <v>0.1615019781279894</v>
       </c>
       <c r="G9" t="n">
         <v>282.4017131910433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04573768641131502</v>
+        <v>0.04570618944793913</v>
       </c>
       <c r="I9" t="n">
-        <v>2274.469686193753</v>
+        <v>10442.73600582091</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>10.78953326634482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03937010000000001</v>
+        <v>0.01222017738070924</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1847827041768386</v>
+        <v>0.1781775961967193</v>
       </c>
       <c r="G10" t="n">
         <v>306.7506264789972</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0210434395004962</v>
+        <v>0.02099686767233633</v>
       </c>
       <c r="I10" t="n">
-        <v>2588.968362117239</v>
+        <v>7688.738528989717</v>
       </c>
     </row>
     <row r="11">
@@ -745,19 +745,19 @@
         <v>12.27959952098016</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0393701</v>
+        <v>0.02673497141856086</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1833959534196968</v>
+        <v>0.1957910299153822</v>
       </c>
       <c r="G11" t="n">
         <v>312.4122327334245</v>
       </c>
       <c r="H11" t="n">
-        <v>0.004945392959949732</v>
+        <v>0.004918295655776306</v>
       </c>
       <c r="I11" t="n">
-        <v>2265.804301883248</v>
+        <v>3742.147805713759</v>
       </c>
     </row>
     <row r="12">
@@ -774,10 +774,10 @@
         <v>12.29250535794931</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03937010000000001</v>
+        <v>0.03490215242997723</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2076483363435291</v>
+        <v>0.1993067342092314</v>
       </c>
       <c r="G12" t="n">
         <v>-12.70530093905245</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2381.00381407354</v>
+        <v>2430.582745717922</v>
       </c>
     </row>
     <row r="13">
@@ -803,19 +803,19 @@
         <v>12.27348826768008</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0393701</v>
+        <v>0.02675001272872714</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1834522276756144</v>
+        <v>0.1958427711307554</v>
       </c>
       <c r="G13" t="n">
         <v>312.2373670356568</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004948010899307982</v>
+        <v>0.004920932871491025</v>
       </c>
       <c r="I13" t="n">
-        <v>2266.733301637856</v>
+        <v>3742.844125606032</v>
       </c>
     </row>
     <row r="14">
@@ -832,19 +832,19 @@
         <v>10.78281312271594</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0393701</v>
+        <v>0.01222335131617269</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1848225771723788</v>
+        <v>0.1782200828630121</v>
       </c>
       <c r="G14" t="n">
         <v>306.6134958703604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0210564619850966</v>
+        <v>0.02100983984178269</v>
       </c>
       <c r="I14" t="n">
-        <v>2590.843850576393</v>
+        <v>7689.729047473157</v>
       </c>
     </row>
     <row r="15">
@@ -861,19 +861,19 @@
         <v>9.932764763690075</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03937010000000002</v>
+        <v>0.005622190702858913</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1509502445468758</v>
+        <v>0.1615511831391808</v>
       </c>
       <c r="G15" t="n">
         <v>282.4660051849108</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04577278403900064</v>
+        <v>0.04574115021390603</v>
       </c>
       <c r="I15" t="n">
-        <v>2276.071403709836</v>
+        <v>10442.73601071107</v>
       </c>
     </row>
     <row r="16">
@@ -890,19 +890,19 @@
         <v>9.111449356179994</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03937010000000002</v>
+        <v>0.009292722870853403</v>
       </c>
       <c r="F16" t="n">
-        <v>0.160296068186784</v>
+        <v>0.151963108058798</v>
       </c>
       <c r="G16" t="n">
         <v>272.3797213132593</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08325352048784469</v>
+        <v>0.08337585985191261</v>
       </c>
       <c r="I16" t="n">
-        <v>2082.017918549884</v>
+        <v>10442.73601068963</v>
       </c>
     </row>
     <row r="17">
@@ -919,19 +919,19 @@
         <v>8.290133948669915</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03937010000000001</v>
+        <v>0.005514163268893766</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1197257689146712</v>
+        <v>0.1303944540163482</v>
       </c>
       <c r="G17" t="n">
         <v>266.0607935717079</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1331143506131333</v>
+        <v>0.1335644011365641</v>
       </c>
       <c r="I17" t="n">
-        <v>1965.462062979232</v>
+        <v>10442.73601069728</v>
       </c>
     </row>
     <row r="18">
@@ -948,19 +948,19 @@
         <v>7.468818541159835</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03937010000000001</v>
+        <v>0.006834741470362862</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1261718447549538</v>
+        <v>0.11815705921726</v>
       </c>
       <c r="G18" t="n">
         <v>256.6456696258964</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1958356894151815</v>
+        <v>0.1968140810442285</v>
       </c>
       <c r="I18" t="n">
-        <v>1803.994218841279</v>
+        <v>10442.73601070992</v>
       </c>
     </row>
     <row r="19">
@@ -977,19 +977,19 @@
         <v>6.647503134649754</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03937010000000003</v>
+        <v>0.004788235391031365</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08306175713833551</v>
+        <v>0.09415729799904884</v>
       </c>
       <c r="G19" t="n">
         <v>247.1852242682867</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2716751788558065</v>
+        <v>0.2734064922487932</v>
       </c>
       <c r="I19" t="n">
-        <v>1563.109586022101</v>
+        <v>10442.73601071448</v>
       </c>
     </row>
     <row r="20">
@@ -1006,19 +1006,19 @@
         <v>5.892053390707112</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03937010000000002</v>
+        <v>0.003937010000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08657831020314619</v>
+        <v>0.07893589376994255</v>
       </c>
       <c r="G20" t="n">
         <v>249.2089720180235</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3601746369066422</v>
+        <v>0.362933118702377</v>
       </c>
       <c r="I20" t="n">
-        <v>1191.193782680512</v>
+        <v>9404.858354175343</v>
       </c>
     </row>
     <row r="21">
@@ -1035,19 +1035,19 @@
         <v>5.359673835222307</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03937010000000003</v>
+        <v>0.003937010000000032</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0393990351620512</v>
+        <v>0.04942172763664562</v>
       </c>
       <c r="G21" t="n">
         <v>220.2977527191311</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4591414724584371</v>
+        <v>0.4633505950346544</v>
       </c>
       <c r="I21" t="n">
-        <v>693.7824515056474</v>
+        <v>5927.862393218332</v>
       </c>
     </row>
     <row r="22">
@@ -1064,19 +1064,19 @@
         <v>4.827294278737503</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03937010000000005</v>
+        <v>0.003937010000000027</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03937010000000003</v>
+        <v>0.02938737640996409</v>
       </c>
       <c r="G22" t="n">
         <v>173.3132649314452</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5648400741826339</v>
+        <v>0.5709154346036752</v>
       </c>
       <c r="I22" t="n">
-        <v>226.6145019852947</v>
+        <v>1940.390619233253</v>
       </c>
     </row>
   </sheetData>
